--- a/backend/catalogues_src/Grade 10 Maths Catalogue.xlsx
+++ b/backend/catalogues_src/Grade 10 Maths Catalogue.xlsx
@@ -2254,7 +2254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L158"/>
+  <dimension ref="B1:L158"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="8.12844036697248" customWidth="1" min="1" max="1"/>
@@ -2262,6 +2262,7 @@
     <col width="30.6238532110092" customWidth="1" min="4" max="12"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="229" t="inlineStr">
         <is>
@@ -2288,22 +2289,22 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="F3" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="G3" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -2313,7 +2314,7 @@
       </c>
       <c r="I3" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="J3" s="111" t="n"/>
@@ -2686,22 +2687,22 @@
       <c r="H24" s="244" t="n"/>
       <c r="I24" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="J24" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="K24" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="L24" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
     </row>
@@ -3016,22 +3017,22 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="E43" s="59" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="F43" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -3041,7 +3042,7 @@
       </c>
       <c r="I43" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="J43" s="111" t="n"/>
@@ -3414,22 +3415,22 @@
       <c r="H64" s="244" t="n"/>
       <c r="I64" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="J64" s="85" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="K64" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="L64" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
     </row>
@@ -3744,22 +3745,22 @@
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="E83" s="89" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="G83" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="H83" s="89" t="inlineStr">
@@ -3769,7 +3770,7 @@
       </c>
       <c r="I83" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="J83" s="111" t="n"/>
@@ -4129,22 +4130,22 @@
       <c r="H103" s="244" t="n"/>
       <c r="I103" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="J103" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="K103" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="L103" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
     </row>
@@ -4459,22 +4460,22 @@
       </c>
       <c r="D122" s="89" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="E122" s="89" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="F122" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="G122" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="H122" s="89" t="inlineStr">
@@ -4484,7 +4485,7 @@
       </c>
       <c r="I122" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="J122" s="112" t="n"/>
@@ -4844,22 +4845,22 @@
       <c r="H142" s="244" t="n"/>
       <c r="I142" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="J142" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="K142" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="L142" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
     </row>
@@ -5246,22 +5247,22 @@
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E3" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F3" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -5271,7 +5272,7 @@
       </c>
       <c r="H3" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I3" s="111" t="n"/>
@@ -5640,22 +5641,22 @@
       <c r="G24" s="244" t="n"/>
       <c r="H24" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I24" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J24" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K24" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
       <c r="L24" s="111" t="n"/>
@@ -5966,22 +5967,22 @@
       <c r="B43" s="58" t="n"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D43" s="59" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E43" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -5991,7 +5992,7 @@
       </c>
       <c r="H43" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I43" s="111" t="n"/>
@@ -6360,22 +6361,22 @@
       <c r="G64" s="244" t="n"/>
       <c r="H64" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I64" s="85" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J64" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K64" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
       <c r="L64" s="111" t="n"/>
@@ -6686,22 +6687,22 @@
       <c r="B83" s="88" t="n"/>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D83" s="89" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F83" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G83" s="89" t="inlineStr">
@@ -6711,7 +6712,7 @@
       </c>
       <c r="H83" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I83" s="111" t="n"/>
@@ -7067,22 +7068,22 @@
       <c r="G103" s="244" t="n"/>
       <c r="H103" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I103" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J103" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K103" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
       <c r="L103" s="111" t="n"/>
@@ -7393,22 +7394,22 @@
       <c r="B122" s="88" t="n"/>
       <c r="C122" s="89" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D122" s="89" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E122" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F122" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G122" s="89" t="inlineStr">
@@ -7418,7 +7419,7 @@
       </c>
       <c r="H122" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I122" s="112" t="n"/>
@@ -7774,22 +7775,22 @@
       <c r="G142" s="244" t="n"/>
       <c r="H142" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I142" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J142" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K142" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
       <c r="L142" s="111" t="n"/>
@@ -8171,22 +8172,22 @@
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E3" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F3" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -8196,7 +8197,7 @@
       </c>
       <c r="H3" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I3" s="111" t="n"/>
@@ -8565,22 +8566,22 @@
       <c r="G24" s="244" t="n"/>
       <c r="H24" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I24" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J24" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K24" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
       <c r="L24" s="111" t="n"/>
@@ -8891,22 +8892,22 @@
       <c r="B43" s="58" t="n"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D43" s="59" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E43" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -8916,7 +8917,7 @@
       </c>
       <c r="H43" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I43" s="111" t="n"/>
@@ -9285,22 +9286,22 @@
       <c r="G64" s="244" t="n"/>
       <c r="H64" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I64" s="85" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J64" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K64" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
       <c r="L64" s="111" t="n"/>
@@ -9611,22 +9612,22 @@
       <c r="B83" s="88" t="n"/>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D83" s="89" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F83" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G83" s="89" t="inlineStr">
@@ -9636,7 +9637,7 @@
       </c>
       <c r="H83" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I83" s="111" t="n"/>
@@ -9992,22 +9993,22 @@
       <c r="G103" s="244" t="n"/>
       <c r="H103" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I103" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J103" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K103" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
       <c r="L103" s="111" t="n"/>
@@ -10318,22 +10319,22 @@
       <c r="B122" s="88" t="n"/>
       <c r="C122" s="89" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D122" s="89" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E122" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F122" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G122" s="89" t="inlineStr">
@@ -10343,7 +10344,7 @@
       </c>
       <c r="H122" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I122" s="112" t="n"/>
@@ -10699,22 +10700,22 @@
       <c r="G142" s="244" t="n"/>
       <c r="H142" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I142" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J142" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K142" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
       <c r="L142" s="111" t="n"/>
@@ -11054,7 +11055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K21"/>
+  <dimension ref="B1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="16.6238532110092" customWidth="1" min="2" max="24"/>
@@ -11081,22 +11082,22 @@
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E3" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F3" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -11106,7 +11107,7 @@
       </c>
       <c r="H3" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I3" s="22" t="n"/>
@@ -11374,7 +11375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M158"/>
+  <dimension ref="B1:M158"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="8.12844036697248" customWidth="1" style="111" min="1" max="1"/>
@@ -11383,6 +11384,7 @@
     <col width="9" customWidth="1" style="111" min="14" max="16384"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="229" t="inlineStr">
         <is>
@@ -11406,22 +11408,22 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="F3" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="G3" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -11431,7 +11433,7 @@
       </c>
       <c r="I3" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
     </row>
@@ -11452,24 +11454,34 @@
         </is>
       </c>
       <c r="C5" s="217" t="n"/>
-      <c r="D5" s="194" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="194" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="194" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" s="194" t="n">
-        <v>7</v>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>8</v>
+      <c r="D5" s="194" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="E5" s="194" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="F5" s="194" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="G5" s="194" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
       </c>
       <c r="I5" s="194" t="inlineStr">
         <is>
-          <t>4, 5, 6</t>
+          <t>Q4, Q5, Q6</t>
         </is>
       </c>
     </row>
@@ -11480,24 +11492,34 @@
         </is>
       </c>
       <c r="C6" s="230" t="n"/>
-      <c r="D6" s="196" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="196" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="196" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" s="196" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" s="12" t="n">
-        <v>8</v>
+      <c r="D6" s="196" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="E6" s="196" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="F6" s="196" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="G6" s="196" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
       </c>
       <c r="I6" s="196" t="inlineStr">
         <is>
-          <t>5, 6, 7</t>
+          <t>Q5, Q6, Q7</t>
         </is>
       </c>
     </row>
@@ -11508,23 +11530,35 @@
         </is>
       </c>
       <c r="C7" s="217" t="n"/>
-      <c r="D7" s="194" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="194" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="194" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" s="194" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="I7" s="194" t="n">
-        <v>5.6</v>
+      <c r="D7" s="194" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="E7" s="194" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="F7" s="194" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="G7" s="194" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="I7" s="194" t="inlineStr">
+        <is>
+          <t>Q5.6</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -11534,26 +11568,34 @@
         </is>
       </c>
       <c r="C8" s="217" t="n"/>
-      <c r="D8" s="194" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="194" t="n">
-        <v>2</v>
+      <c r="D8" s="194" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="E8" s="194" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
       </c>
       <c r="F8" s="194" t="inlineStr">
         <is>
-          <t>3, 4</t>
-        </is>
-      </c>
-      <c r="G8" s="194" t="n">
-        <v>7</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>8</v>
+          <t>Q3, Q4</t>
+        </is>
+      </c>
+      <c r="G8" s="194" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
       </c>
       <c r="I8" s="194" t="inlineStr">
         <is>
-          <t>5, 6</t>
+          <t>Q5, Q6</t>
         </is>
       </c>
     </row>
@@ -11564,24 +11606,34 @@
         </is>
       </c>
       <c r="C9" s="217" t="n"/>
-      <c r="D9" s="194" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="194" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="194" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" s="194" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>7</v>
+      <c r="D9" s="194" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="E9" s="194" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="F9" s="194" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="G9" s="194" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
       </c>
       <c r="I9" s="194" t="inlineStr">
         <is>
-          <t>5, 6</t>
+          <t>Q5, Q6</t>
         </is>
       </c>
     </row>
@@ -11739,6 +11791,7 @@
       <c r="H20" s="46" t="n"/>
       <c r="I20" s="45" t="n"/>
     </row>
+    <row r="21"/>
     <row r="22" ht="15" customHeight="1">
       <c r="B22" s="229" t="inlineStr">
         <is>
@@ -11807,22 +11860,22 @@
       <c r="H24" s="244" t="n"/>
       <c r="I24" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="J24" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="K24" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="L24" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
     </row>
@@ -11835,28 +11888,40 @@
       <c r="C25" s="217" t="n"/>
       <c r="D25" s="194" t="inlineStr">
         <is>
-          <t>1, 2</t>
-        </is>
-      </c>
-      <c r="E25" s="194" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" s="194" t="n">
-        <v>9</v>
+          <t>Q1, Q2</t>
+        </is>
+      </c>
+      <c r="E25" s="194" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F25" s="194" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
       </c>
       <c r="G25" s="194" t="n"/>
-      <c r="H25" s="213" t="n">
-        <v>7</v>
-      </c>
-      <c r="I25" s="223" t="n">
-        <v>4</v>
-      </c>
-      <c r="J25" s="182" t="n">
-        <v>5</v>
+      <c r="H25" s="213" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="I25" s="223" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="J25" s="182" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
       </c>
       <c r="K25" s="182" t="n"/>
-      <c r="L25" s="183" t="n">
-        <v>6</v>
+      <c r="L25" s="183" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -11868,30 +11933,40 @@
       <c r="C26" s="230" t="n"/>
       <c r="D26" s="196" t="inlineStr">
         <is>
-          <t>1, 2</t>
-        </is>
-      </c>
-      <c r="E26" s="196" t="n">
-        <v>3</v>
+          <t>Q1, Q2</t>
+        </is>
+      </c>
+      <c r="E26" s="196" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
       </c>
       <c r="F26" s="196" t="inlineStr">
         <is>
-          <t>8, 9</t>
+          <t>Q8, Q9</t>
         </is>
       </c>
       <c r="G26" s="196" t="n"/>
-      <c r="H26" s="214" t="n">
-        <v>7</v>
-      </c>
-      <c r="I26" s="224" t="n">
-        <v>4</v>
-      </c>
-      <c r="J26" s="198" t="n">
-        <v>5</v>
+      <c r="H26" s="214" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="I26" s="224" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="J26" s="198" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
       </c>
       <c r="K26" s="198" t="n"/>
-      <c r="L26" s="199" t="n">
-        <v>6</v>
+      <c r="L26" s="199" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -11901,28 +11976,42 @@
         </is>
       </c>
       <c r="C27" s="230" t="n"/>
-      <c r="D27" s="194" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E27" s="194" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" s="194" t="n">
-        <v>8.9</v>
+      <c r="D27" s="194" t="inlineStr">
+        <is>
+          <t>Q1.2</t>
+        </is>
+      </c>
+      <c r="E27" s="194" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F27" s="194" t="inlineStr">
+        <is>
+          <t>Q8.9</t>
+        </is>
       </c>
       <c r="G27" s="194" t="n"/>
-      <c r="H27" s="213" t="n">
-        <v>7</v>
-      </c>
-      <c r="I27" s="224" t="n">
-        <v>4</v>
+      <c r="H27" s="213" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="I27" s="224" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
       </c>
       <c r="J27" s="198" t="n"/>
-      <c r="K27" s="198" t="n">
-        <v>6</v>
-      </c>
-      <c r="L27" s="199" t="n">
-        <v>5</v>
+      <c r="K27" s="198" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="L27" s="199" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -11932,36 +12021,46 @@
         </is>
       </c>
       <c r="C28" s="217" t="n"/>
-      <c r="D28" s="194" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="194" t="n">
-        <v>2</v>
+      <c r="D28" s="194" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="E28" s="194" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
       </c>
       <c r="F28" s="194" t="inlineStr">
         <is>
-          <t>7, 8</t>
+          <t>Q7, Q8</t>
         </is>
       </c>
       <c r="G28" s="194" t="n"/>
-      <c r="H28" s="213" t="n">
-        <v>6</v>
-      </c>
-      <c r="I28" s="224" t="n">
-        <v>3</v>
+      <c r="H28" s="213" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="I28" s="224" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
       </c>
       <c r="J28" s="198" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>Q4.2</t>
         </is>
       </c>
       <c r="K28" s="198" t="inlineStr">
         <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="L28" s="199" t="n">
-        <v>5</v>
+          <t>Q4.1</t>
+        </is>
+      </c>
+      <c r="L28" s="199" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -12168,6 +12267,7 @@
       <c r="K40" s="83" t="n"/>
       <c r="L40" s="84" t="n"/>
     </row>
+    <row r="41"/>
     <row r="42" ht="15" customHeight="1">
       <c r="B42" s="229" t="inlineStr">
         <is>
@@ -12191,22 +12291,22 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="F43" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="G43" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -12216,7 +12316,7 @@
       </c>
       <c r="I43" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
     </row>
@@ -12454,6 +12554,7 @@
       <c r="H60" s="45" t="n"/>
       <c r="I60" s="164" t="n"/>
     </row>
+    <row r="61"/>
     <row r="62" ht="15" customHeight="1">
       <c r="B62" s="229" t="inlineStr">
         <is>
@@ -12522,22 +12623,22 @@
       <c r="H64" s="244" t="n"/>
       <c r="I64" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="J64" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="K64" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="L64" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
     </row>
@@ -12813,6 +12914,7 @@
       <c r="K80" s="83" t="n"/>
       <c r="L80" s="84" t="n"/>
     </row>
+    <row r="81"/>
     <row r="82" ht="15" customHeight="1">
       <c r="B82" s="229" t="inlineStr">
         <is>
@@ -12836,22 +12938,22 @@
       </c>
       <c r="D83" s="89" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="E83" s="89" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="F83" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="G83" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="H83" s="89" t="inlineStr">
@@ -12861,7 +12963,7 @@
       </c>
       <c r="I83" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
     </row>
@@ -13089,6 +13191,7 @@
       <c r="H99" s="45" t="n"/>
       <c r="I99" s="164" t="n"/>
     </row>
+    <row r="100"/>
     <row r="101" ht="15" customHeight="1">
       <c r="B101" s="229" t="inlineStr">
         <is>
@@ -13157,22 +13260,22 @@
       <c r="H103" s="244" t="n"/>
       <c r="I103" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="J103" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="K103" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="L103" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
     </row>
@@ -13448,6 +13551,7 @@
       <c r="K119" s="83" t="n"/>
       <c r="L119" s="84" t="n"/>
     </row>
+    <row r="120"/>
     <row r="121">
       <c r="B121" s="229" t="inlineStr">
         <is>
@@ -13475,22 +13579,22 @@
       </c>
       <c r="D122" s="89" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="E122" s="89" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="F122" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="G122" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="H122" s="89" t="inlineStr">
@@ -13500,7 +13604,7 @@
       </c>
       <c r="I122" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="J122" s="112" t="n"/>
@@ -13776,6 +13880,7 @@
       <c r="H138" s="45" t="n"/>
       <c r="I138" s="164" t="n"/>
     </row>
+    <row r="139"/>
     <row r="140" ht="15" customHeight="1">
       <c r="B140" s="229" t="inlineStr">
         <is>
@@ -13844,22 +13949,22 @@
       <c r="H142" s="244" t="n"/>
       <c r="I142" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="J142" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="K142" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="L142" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
     </row>
@@ -14205,7 +14310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K158"/>
+  <dimension ref="B1:K158"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.12844036697248" defaultRowHeight="14.25"/>
   <cols>
     <col width="8.12844036697248" customWidth="1" style="111" min="1" max="1"/>
@@ -14232,22 +14337,22 @@
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E3" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F3" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -14257,7 +14362,7 @@
       </c>
       <c r="H3" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
     </row>
@@ -14537,22 +14642,22 @@
       <c r="G24" s="244" t="n"/>
       <c r="H24" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I24" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J24" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K24" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
     </row>
@@ -14830,22 +14935,22 @@
       <c r="B43" s="58" t="n"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D43" s="59" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E43" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -14855,7 +14960,7 @@
       </c>
       <c r="H43" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
     </row>
@@ -14890,11 +14995,15 @@
       <c r="C46" s="196" t="n"/>
       <c r="D46" s="12" t="n"/>
       <c r="E46" s="196" t="n"/>
-      <c r="F46" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="G46" s="196" t="n">
-        <v>5</v>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="G46" s="196" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
       </c>
       <c r="H46" s="186" t="n"/>
     </row>
@@ -14907,8 +15016,10 @@
       <c r="C47" s="194" t="n"/>
       <c r="D47" s="15" t="n"/>
       <c r="E47" s="194" t="n"/>
-      <c r="F47" s="15" t="n">
-        <v>3</v>
+      <c r="F47" s="15" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
       </c>
       <c r="G47" s="194" t="n"/>
       <c r="H47" s="141" t="n"/>
@@ -14922,8 +15033,10 @@
       <c r="C48" s="194" t="n"/>
       <c r="D48" s="15" t="n"/>
       <c r="E48" s="194" t="n"/>
-      <c r="F48" s="15" t="n">
-        <v>2</v>
+      <c r="F48" s="15" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
       </c>
       <c r="G48" s="194" t="n"/>
       <c r="H48" s="141" t="n"/>
@@ -14937,11 +15050,15 @@
       <c r="C49" s="194" t="n"/>
       <c r="D49" s="15" t="n"/>
       <c r="E49" s="194" t="n"/>
-      <c r="F49" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="194" t="n">
-        <v>2</v>
+      <c r="F49" s="15" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="G49" s="194" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
       </c>
       <c r="H49" s="141" t="n"/>
     </row>
@@ -15147,22 +15264,22 @@
       <c r="G64" s="244" t="n"/>
       <c r="H64" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I64" s="85" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J64" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K64" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
     </row>
@@ -15189,21 +15306,29 @@
         </is>
       </c>
       <c r="C66" s="120" t="n"/>
-      <c r="D66" s="121" t="n">
-        <v>6</v>
+      <c r="D66" s="121" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
       </c>
       <c r="E66" s="98" t="n"/>
       <c r="F66" s="121" t="n"/>
       <c r="G66" s="120" t="n"/>
-      <c r="H66" s="195" t="n">
-        <v>2</v>
-      </c>
-      <c r="I66" s="143" t="n">
-        <v>1</v>
+      <c r="H66" s="195" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="I66" s="143" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
       </c>
       <c r="J66" s="198" t="n"/>
-      <c r="K66" s="199" t="n">
-        <v>3</v>
+      <c r="K66" s="199" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -15212,24 +15337,34 @@
           <t>Sept_2017</t>
         </is>
       </c>
-      <c r="C67" s="194" t="n">
-        <v>2</v>
-      </c>
-      <c r="D67" s="15" t="n">
-        <v>1</v>
+      <c r="C67" s="194" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D67" s="15" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
       </c>
       <c r="E67" s="194" t="n"/>
       <c r="F67" s="15" t="n"/>
       <c r="G67" s="194" t="n"/>
       <c r="H67" s="195" t="n"/>
-      <c r="I67" s="143" t="n">
-        <v>4</v>
-      </c>
-      <c r="J67" s="198" t="n">
-        <v>5</v>
-      </c>
-      <c r="K67" s="199" t="n">
-        <v>6</v>
+      <c r="I67" s="143" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="J67" s="198" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="K67" s="199" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -15238,23 +15373,33 @@
           <t>Sept_2018</t>
         </is>
       </c>
-      <c r="C68" s="98" t="n">
-        <v>5</v>
-      </c>
-      <c r="D68" s="97" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" s="98" t="n">
-        <v>3</v>
+      <c r="C68" s="98" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="D68" s="97" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="E68" s="98" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
       </c>
       <c r="F68" s="97" t="n"/>
-      <c r="G68" s="98" t="n">
-        <v>4</v>
+      <c r="G68" s="98" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
       </c>
       <c r="H68" s="195" t="n"/>
       <c r="I68" s="143" t="n"/>
-      <c r="J68" s="198" t="n">
-        <v>6</v>
+      <c r="J68" s="198" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
       </c>
       <c r="K68" s="199" t="n"/>
     </row>
@@ -15266,19 +15411,23 @@
       </c>
       <c r="C69" s="98" t="inlineStr">
         <is>
-          <t>3, 4</t>
+          <t>Q3, Q4</t>
         </is>
       </c>
       <c r="D69" s="97" t="n"/>
       <c r="E69" s="98" t="n"/>
       <c r="F69" s="97" t="n"/>
-      <c r="G69" s="98" t="n">
-        <v>6</v>
+      <c r="G69" s="98" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
       </c>
       <c r="H69" s="195" t="n"/>
       <c r="I69" s="143" t="n"/>
-      <c r="J69" s="198" t="n">
-        <v>5</v>
+      <c r="J69" s="198" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
       </c>
       <c r="K69" s="199" t="n"/>
     </row>
@@ -15476,22 +15625,22 @@
       <c r="B83" s="88" t="n"/>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D83" s="89" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F83" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G83" s="89" t="inlineStr">
@@ -15501,7 +15650,7 @@
       </c>
       <c r="H83" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
     </row>
@@ -15524,22 +15673,26 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C85" s="196" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" s="12" t="n">
-        <v>2</v>
+      <c r="C85" s="196" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
       </c>
       <c r="E85" s="196" t="inlineStr">
         <is>
-          <t>3, 4</t>
+          <t>Q3, Q4</t>
         </is>
       </c>
       <c r="F85" s="12" t="n"/>
       <c r="G85" s="196" t="n"/>
       <c r="H85" s="186" t="inlineStr">
         <is>
-          <t>5, 6</t>
+          <t>Q5, Q6</t>
         </is>
       </c>
     </row>
@@ -15549,20 +15702,26 @@
           <t>May/Jun_2017</t>
         </is>
       </c>
-      <c r="C86" s="194" t="n">
-        <v>1</v>
-      </c>
-      <c r="D86" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E86" s="194" t="n">
-        <v>3</v>
+      <c r="C86" s="194" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D86" s="15" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E86" s="194" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
       </c>
       <c r="F86" s="15" t="n"/>
       <c r="G86" s="194" t="n"/>
       <c r="H86" s="141" t="inlineStr">
         <is>
-          <t>4, 5, 6</t>
+          <t>Q4, Q5, Q6</t>
         </is>
       </c>
     </row>
@@ -15572,20 +15731,26 @@
           <t>May/Jun_2018</t>
         </is>
       </c>
-      <c r="C87" s="194" t="n">
-        <v>1</v>
-      </c>
-      <c r="D87" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E87" s="194" t="n">
-        <v>3</v>
+      <c r="C87" s="194" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D87" s="15" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E87" s="194" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
       </c>
       <c r="F87" s="15" t="n"/>
       <c r="G87" s="194" t="n"/>
       <c r="H87" s="141" t="inlineStr">
         <is>
-          <t>4, 5</t>
+          <t>Q4, Q5</t>
         </is>
       </c>
     </row>
@@ -15804,22 +15969,22 @@
       <c r="G103" s="244" t="n"/>
       <c r="H103" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I103" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J103" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K103" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
     </row>
@@ -15849,7 +16014,7 @@
       <c r="D105" s="120" t="n"/>
       <c r="E105" s="98" t="inlineStr">
         <is>
-          <t>7, 8</t>
+          <t>Q7, Q8</t>
         </is>
       </c>
       <c r="F105" s="120" t="n"/>
@@ -15869,7 +16034,7 @@
       <c r="D106" s="98" t="n"/>
       <c r="E106" s="98" t="inlineStr">
         <is>
-          <t>7, 8</t>
+          <t>Q7, Q8</t>
         </is>
       </c>
       <c r="F106" s="98" t="n"/>
@@ -15887,24 +16052,28 @@
       </c>
       <c r="C107" s="194" t="n"/>
       <c r="D107" s="194" t="n"/>
-      <c r="E107" s="194" t="n">
-        <v>8</v>
+      <c r="E107" s="194" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
       </c>
       <c r="F107" s="194" t="n"/>
       <c r="G107" s="194" t="n"/>
       <c r="H107" s="195" t="inlineStr">
         <is>
-          <t>6.1-6.4</t>
+          <t>Q6.1, Q6.2, Q6.3, Q6.4</t>
         </is>
       </c>
       <c r="I107" s="198" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>Q6.5</t>
         </is>
       </c>
       <c r="J107" s="198" t="n"/>
-      <c r="K107" s="199" t="n">
-        <v>7</v>
+      <c r="K107" s="199" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -15914,28 +16083,32 @@
         </is>
       </c>
       <c r="C108" s="194" t="n"/>
-      <c r="D108" s="194" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" s="194" t="n">
-        <v>3</v>
+      <c r="D108" s="194" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="E108" s="194" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
       </c>
       <c r="F108" s="194" t="n"/>
       <c r="G108" s="194" t="n"/>
       <c r="H108" s="195" t="inlineStr">
         <is>
-          <t>2.1, 2.2, 2.3, 2.5</t>
+          <t>Q2.1, Q2.2, Q2.3, Q2.5</t>
         </is>
       </c>
       <c r="I108" s="198" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>Q2.4</t>
         </is>
       </c>
       <c r="J108" s="198" t="n"/>
       <c r="K108" s="199" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>Q2.6</t>
         </is>
       </c>
     </row>
@@ -16136,22 +16309,22 @@
       <c r="B122" s="88" t="n"/>
       <c r="C122" s="89" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D122" s="89" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E122" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F122" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G122" s="89" t="inlineStr">
@@ -16161,7 +16334,7 @@
       </c>
       <c r="H122" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I122" s="112" t="n"/>
@@ -16238,12 +16411,14 @@
           <t>Feb/Mar_2019</t>
         </is>
       </c>
-      <c r="C127" s="194" t="n">
-        <v>1</v>
+      <c r="C127" s="194" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
       </c>
       <c r="D127" s="194" t="inlineStr">
         <is>
-          <t>2, 3, 4</t>
+          <t>Q2, Q3, Q4</t>
         </is>
       </c>
       <c r="E127" s="194" t="n"/>
@@ -16294,12 +16469,12 @@
       </c>
       <c r="C130" s="194" t="inlineStr">
         <is>
-          <t>1.3, 1.6, 1.7, 1.8, 2</t>
+          <t>Q1.3, Q1.6, Q1.7, Q1.8, Q2</t>
         </is>
       </c>
       <c r="D130" s="194" t="inlineStr">
         <is>
-          <t>1.4, 1.5, 3</t>
+          <t>Q1.4, Q1.5, Q3</t>
         </is>
       </c>
       <c r="E130" s="194" t="n"/>
@@ -16482,22 +16657,22 @@
       <c r="G142" s="244" t="n"/>
       <c r="H142" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I142" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J142" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K142" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
     </row>
@@ -16575,7 +16750,7 @@
       <c r="D147" s="194" t="n"/>
       <c r="E147" s="194" t="inlineStr">
         <is>
-          <t>5, 6, 7, 8</t>
+          <t>Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="F147" s="194" t="n"/>
@@ -16627,7 +16802,7 @@
       <c r="D150" s="194" t="n"/>
       <c r="E150" s="194" t="inlineStr">
         <is>
-          <t>1.9, 1.10, 4, 5</t>
+          <t>Q1.9, Q1.10, Q4, Q5</t>
         </is>
       </c>
       <c r="F150" s="194" t="n"/>
@@ -16855,22 +17030,22 @@
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D3" s="146" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E3" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -16880,7 +17055,7 @@
       </c>
       <c r="H3" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
     </row>
@@ -16990,24 +17165,34 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="194" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="194" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="G12" s="194" t="n">
-        <v>7</v>
+      <c r="C12" s="194" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E12" s="194" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="G12" s="194" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
       </c>
       <c r="H12" s="141" t="inlineStr">
         <is>
-          <t>4, 5</t>
+          <t>Q4, Q5</t>
         </is>
       </c>
     </row>
@@ -17174,22 +17359,22 @@
       <c r="G24" s="244" t="n"/>
       <c r="H24" s="161" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I24" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J24" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K24" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
     </row>
@@ -17313,36 +17498,44 @@
       </c>
       <c r="C32" s="194" t="inlineStr">
         <is>
-          <t>1, 2</t>
-        </is>
-      </c>
-      <c r="D32" s="15" t="n">
-        <v>3</v>
+          <t>Q1, Q2</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
       </c>
       <c r="E32" s="194" t="inlineStr">
         <is>
-          <t>8, 9, 10</t>
+          <t>Q8, Q9, Q10</t>
         </is>
       </c>
       <c r="F32" s="15" t="n"/>
-      <c r="G32" s="194" t="n">
-        <v>7</v>
+      <c r="G32" s="194" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
       </c>
       <c r="H32" s="195" t="inlineStr">
         <is>
-          <t>4.1, 5.1</t>
+          <t>Q4.1, Q5.1</t>
         </is>
       </c>
       <c r="I32" s="143" t="inlineStr">
         <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="J32" s="198" t="n">
-        <v>5</v>
-      </c>
-      <c r="K32" s="199" t="n">
-        <v>6</v>
+          <t>Q4.2</t>
+        </is>
+      </c>
+      <c r="J32" s="198" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="K32" s="199" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -17491,22 +17684,22 @@
       <c r="B43" s="58" t="n"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D43" s="59" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E43" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -17516,7 +17709,7 @@
       </c>
       <c r="H43" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
     </row>
@@ -17796,22 +17989,22 @@
       <c r="G64" s="244" t="n"/>
       <c r="H64" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I64" s="85" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J64" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K64" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
     </row>
@@ -18090,22 +18283,22 @@
       <c r="B83" s="58" t="n"/>
       <c r="C83" s="167" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E83" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F83" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -18115,7 +18308,7 @@
       </c>
       <c r="H83" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I83" s="89" t="inlineStr">
@@ -18154,22 +18347,32 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C86" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D86" s="196" t="n">
-        <v>3</v>
-      </c>
-      <c r="E86" s="196" t="n">
-        <v>4</v>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D86" s="196" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="E86" s="196" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
       </c>
       <c r="F86" s="12" t="n"/>
       <c r="G86" s="196" t="n"/>
-      <c r="H86" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I86" s="196" t="n">
-        <v>1</v>
+      <c r="H86" s="12" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="I86" s="196" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -18180,24 +18383,30 @@
       </c>
       <c r="C87" s="15" t="inlineStr">
         <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D87" s="194" t="n">
-        <v>4</v>
-      </c>
-      <c r="E87" s="194" t="n">
-        <v>5</v>
+          <t>Q2, Q3</t>
+        </is>
+      </c>
+      <c r="D87" s="194" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="E87" s="194" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
       </c>
       <c r="F87" s="15" t="n"/>
       <c r="G87" s="194" t="n"/>
       <c r="H87" s="15" t="inlineStr">
         <is>
-          <t>6, 7</t>
-        </is>
-      </c>
-      <c r="I87" s="194" t="n">
-        <v>1</v>
+          <t>Q6, Q7</t>
+        </is>
+      </c>
+      <c r="I87" s="194" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
       </c>
     </row>
     <row r="88" ht="14.95" customHeight="1">
@@ -18206,22 +18415,32 @@
           <t>May/Jun_2018</t>
         </is>
       </c>
-      <c r="C88" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D88" s="194" t="n">
-        <v>3</v>
-      </c>
-      <c r="E88" s="194" t="n">
-        <v>4</v>
+      <c r="C88" s="15" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D88" s="194" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="E88" s="194" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
       </c>
       <c r="F88" s="15" t="n"/>
       <c r="G88" s="194" t="n"/>
-      <c r="H88" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="I88" s="194" t="n">
-        <v>1</v>
+      <c r="H88" s="15" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="I88" s="194" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -18230,19 +18449,27 @@
           <t>May/Jun_2019</t>
         </is>
       </c>
-      <c r="C89" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D89" s="194" t="n">
-        <v>2</v>
-      </c>
-      <c r="E89" s="194" t="n">
-        <v>3</v>
+      <c r="C89" s="15" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D89" s="194" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E89" s="194" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
       </c>
       <c r="F89" s="15" t="n"/>
       <c r="G89" s="194" t="n"/>
-      <c r="H89" s="15" t="n">
-        <v>4</v>
+      <c r="H89" s="15" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
       </c>
       <c r="I89" s="194" t="n"/>
     </row>
@@ -18445,22 +18672,22 @@
       <c r="G103" s="244" t="n"/>
       <c r="H103" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I103" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J103" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K103" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
     </row>
@@ -18490,21 +18717,25 @@
       <c r="D105" s="196" t="n"/>
       <c r="E105" s="194" t="inlineStr">
         <is>
-          <t>5, 6, 7</t>
+          <t>Q5, Q6, Q7</t>
         </is>
       </c>
       <c r="F105" s="196" t="n"/>
       <c r="G105" s="196" t="n"/>
       <c r="H105" s="195" t="inlineStr">
         <is>
-          <t>1, 2</t>
-        </is>
-      </c>
-      <c r="I105" s="143" t="n">
-        <v>3</v>
-      </c>
-      <c r="J105" s="198" t="n">
-        <v>4</v>
+          <t>Q1, Q2</t>
+        </is>
+      </c>
+      <c r="I105" s="143" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="J105" s="198" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
       </c>
       <c r="K105" s="199" t="n"/>
     </row>
@@ -18518,22 +18749,26 @@
       <c r="D106" s="194" t="n"/>
       <c r="E106" s="194" t="inlineStr">
         <is>
-          <t>5, 6</t>
+          <t>Q5, Q6</t>
         </is>
       </c>
       <c r="F106" s="194" t="n"/>
       <c r="G106" s="194" t="n"/>
       <c r="H106" s="195" t="inlineStr">
         <is>
-          <t>1, 2</t>
-        </is>
-      </c>
-      <c r="I106" s="143" t="n">
-        <v>3</v>
+          <t>Q1, Q2</t>
+        </is>
+      </c>
+      <c r="I106" s="143" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
       </c>
       <c r="J106" s="198" t="n"/>
-      <c r="K106" s="199" t="n">
-        <v>4</v>
+      <c r="K106" s="199" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -18546,18 +18781,20 @@
       <c r="D107" s="194" t="n"/>
       <c r="E107" s="194" t="inlineStr">
         <is>
-          <t>4, 5</t>
+          <t>Q4, Q5</t>
         </is>
       </c>
       <c r="F107" s="194" t="n"/>
       <c r="G107" s="194" t="n"/>
       <c r="H107" s="195" t="inlineStr">
         <is>
-          <t>1, 2</t>
-        </is>
-      </c>
-      <c r="I107" s="143" t="n">
-        <v>3</v>
+          <t>Q1, Q2</t>
+        </is>
+      </c>
+      <c r="I107" s="143" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
       </c>
       <c r="J107" s="198" t="n"/>
       <c r="K107" s="199" t="n"/>
@@ -18569,29 +18806,33 @@
         </is>
       </c>
       <c r="C108" s="194" t="n"/>
-      <c r="D108" s="194" t="n">
-        <v>4</v>
+      <c r="D108" s="194" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
       </c>
       <c r="E108" s="194" t="inlineStr">
         <is>
-          <t>5, 6</t>
+          <t>Q5, Q6</t>
         </is>
       </c>
       <c r="F108" s="194" t="n"/>
       <c r="G108" s="194" t="n"/>
       <c r="H108" s="195" t="inlineStr">
         <is>
-          <t>1, 2.1, 2.3</t>
+          <t>Q1, Q2.1, Q2.3</t>
         </is>
       </c>
       <c r="I108" s="143" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>Q2.2</t>
         </is>
       </c>
       <c r="J108" s="198" t="n"/>
-      <c r="K108" s="199" t="n">
-        <v>3</v>
+      <c r="K108" s="199" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -18791,22 +19032,22 @@
       <c r="B122" s="88" t="n"/>
       <c r="C122" s="89" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D122" s="89" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E122" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F122" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G122" s="89" t="inlineStr">
@@ -18816,7 +19057,7 @@
       </c>
       <c r="H122" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I122" s="112" t="n"/>
@@ -19123,22 +19364,22 @@
       <c r="G142" s="244" t="n"/>
       <c r="H142" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I142" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J142" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K142" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
     </row>
@@ -19469,7 +19710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K159"/>
+  <dimension ref="B1:K159"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.12844036697248" defaultRowHeight="14.25"/>
   <cols>
     <col width="8.12844036697248" customWidth="1" style="111" min="1" max="1"/>
@@ -19496,22 +19737,22 @@
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E3" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F3" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -19521,7 +19762,7 @@
       </c>
       <c r="H3" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
     </row>
@@ -19801,22 +20042,22 @@
       <c r="G24" s="244" t="n"/>
       <c r="H24" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I24" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J24" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K24" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
     </row>
@@ -20094,22 +20335,22 @@
       <c r="B43" s="58" t="n"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D43" s="59" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E43" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -20119,7 +20360,7 @@
       </c>
       <c r="H43" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
     </row>
@@ -20399,22 +20640,22 @@
       <c r="G64" s="244" t="n"/>
       <c r="H64" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I64" s="85" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J64" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K64" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
     </row>
@@ -20692,22 +20933,22 @@
       <c r="B83" s="236" t="n"/>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
@@ -20717,7 +20958,7 @@
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
@@ -20770,22 +21011,32 @@
           <t>May/Jun_2017</t>
         </is>
       </c>
-      <c r="C87" s="194" t="n">
-        <v>2</v>
-      </c>
-      <c r="D87" s="194" t="n">
-        <v>3</v>
-      </c>
-      <c r="E87" s="194" t="n">
-        <v>4</v>
-      </c>
-      <c r="F87" s="194" t="n">
-        <v>5</v>
+      <c r="C87" s="194" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D87" s="194" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="E87" s="194" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="F87" s="194" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
       </c>
       <c r="G87" s="194" t="n"/>
       <c r="H87" s="194" t="n"/>
-      <c r="I87" s="141" t="n">
-        <v>1</v>
+      <c r="I87" s="141" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -20794,24 +21045,32 @@
           <t>May/Jun_2018</t>
         </is>
       </c>
-      <c r="C88" s="194" t="n">
-        <v>2</v>
-      </c>
-      <c r="D88" s="194" t="n">
-        <v>3</v>
-      </c>
-      <c r="E88" s="194" t="n">
-        <v>4</v>
+      <c r="C88" s="194" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D88" s="194" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="E88" s="194" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
       </c>
       <c r="F88" s="194" t="n"/>
       <c r="G88" s="194" t="n"/>
       <c r="H88" s="194" t="inlineStr">
         <is>
-          <t>5, 6</t>
-        </is>
-      </c>
-      <c r="I88" s="141" t="n">
-        <v>1</v>
+          <t>Q5, Q6</t>
+        </is>
+      </c>
+      <c r="I88" s="141" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
       </c>
     </row>
     <row r="89" ht="14.95" customHeight="1">
@@ -20820,22 +21079,32 @@
           <t>May/Jun_2019</t>
         </is>
       </c>
-      <c r="C89" s="194" t="n">
-        <v>2</v>
-      </c>
-      <c r="D89" s="194" t="n">
-        <v>3</v>
-      </c>
-      <c r="E89" s="194" t="n">
-        <v>4</v>
+      <c r="C89" s="194" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D89" s="194" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="E89" s="194" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
       </c>
       <c r="F89" s="194" t="n"/>
       <c r="G89" s="194" t="n"/>
-      <c r="H89" s="194" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I89" s="141" t="n">
-        <v>1</v>
+      <c r="H89" s="194" t="inlineStr">
+        <is>
+          <t>Q5.6</t>
+        </is>
+      </c>
+      <c r="I89" s="141" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -21051,22 +21320,22 @@
       <c r="G104" s="244" t="n"/>
       <c r="H104" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I104" s="85" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J104" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K104" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
     </row>
@@ -21112,22 +21381,30 @@
       <c r="D107" s="15" t="n"/>
       <c r="E107" s="194" t="inlineStr">
         <is>
-          <t>5, 6</t>
+          <t>Q5, Q6</t>
         </is>
       </c>
       <c r="F107" s="15" t="n"/>
       <c r="G107" s="194" t="n"/>
-      <c r="H107" s="195" t="n">
-        <v>1</v>
-      </c>
-      <c r="I107" s="143" t="n">
-        <v>2</v>
-      </c>
-      <c r="J107" s="198" t="n">
-        <v>3</v>
-      </c>
-      <c r="K107" s="199" t="n">
-        <v>4</v>
+      <c r="H107" s="195" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="I107" s="143" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="J107" s="198" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="K107" s="199" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -21140,28 +21417,30 @@
       <c r="D108" s="15" t="n"/>
       <c r="E108" s="194" t="inlineStr">
         <is>
-          <t>5, 6</t>
+          <t>Q5, Q6</t>
         </is>
       </c>
       <c r="F108" s="15" t="n"/>
       <c r="G108" s="194" t="n"/>
       <c r="H108" s="195" t="inlineStr">
         <is>
-          <t>1.1, 1.3, 2.1</t>
+          <t>Q1.1, Q1.3, Q2.1</t>
         </is>
       </c>
       <c r="I108" s="143" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>Q1.2</t>
         </is>
       </c>
       <c r="J108" s="198" t="inlineStr">
         <is>
-          <t>2.2, 3</t>
-        </is>
-      </c>
-      <c r="K108" s="199" t="n">
-        <v>4</v>
+          <t>Q2.2, Q3</t>
+        </is>
+      </c>
+      <c r="K108" s="199" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -21171,24 +21450,26 @@
         </is>
       </c>
       <c r="C109" s="194" t="n"/>
-      <c r="D109" s="15" t="n">
-        <v>1</v>
+      <c r="D109" s="15" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
       </c>
       <c r="E109" s="194" t="inlineStr">
         <is>
-          <t>4, 5</t>
+          <t>Q4, Q5</t>
         </is>
       </c>
       <c r="F109" s="15" t="n"/>
       <c r="G109" s="194" t="n"/>
       <c r="H109" s="195" t="inlineStr">
         <is>
-          <t>2.1, 3</t>
+          <t>Q2.1, Q3</t>
         </is>
       </c>
       <c r="I109" s="143" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>Q2.2</t>
         </is>
       </c>
       <c r="J109" s="198" t="n"/>
@@ -21391,22 +21672,22 @@
       <c r="B123" s="88" t="n"/>
       <c r="C123" s="89" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D123" s="89" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E123" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F123" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G123" s="89" t="inlineStr">
@@ -21416,7 +21697,7 @@
       </c>
       <c r="H123" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I123" s="112" t="n"/>
@@ -21723,22 +22004,22 @@
       <c r="G143" s="244" t="n"/>
       <c r="H143" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I143" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J143" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K143" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
     </row>
@@ -22111,22 +22392,22 @@
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E3" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F3" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -22136,7 +22417,7 @@
       </c>
       <c r="H3" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I3" s="111" t="n"/>
@@ -22505,22 +22786,22 @@
       <c r="G24" s="244" t="n"/>
       <c r="H24" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I24" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J24" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K24" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
       <c r="L24" s="111" t="n"/>
@@ -22882,22 +23163,22 @@
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E3" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F3" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -22907,7 +23188,7 @@
       </c>
       <c r="H3" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I3" s="111" t="n"/>
@@ -23276,22 +23557,22 @@
       <c r="G24" s="244" t="n"/>
       <c r="H24" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I24" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J24" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K24" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
       <c r="L24" s="111" t="n"/>
@@ -23602,22 +23883,22 @@
       <c r="B43" s="58" t="n"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D43" s="59" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E43" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -23627,7 +23908,7 @@
       </c>
       <c r="H43" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I43" s="111" t="n"/>
@@ -23996,22 +24277,22 @@
       <c r="G64" s="244" t="n"/>
       <c r="H64" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I64" s="85" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J64" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K64" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
       <c r="L64" s="111" t="n"/>
@@ -24322,22 +24603,22 @@
       <c r="B83" s="88" t="n"/>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D83" s="89" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F83" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G83" s="89" t="inlineStr">
@@ -24347,7 +24628,7 @@
       </c>
       <c r="H83" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I83" s="111" t="n"/>
@@ -24703,22 +24984,22 @@
       <c r="G103" s="244" t="n"/>
       <c r="H103" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I103" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J103" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K103" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
       <c r="L103" s="111" t="n"/>
@@ -25029,22 +25310,22 @@
       <c r="B122" s="88" t="n"/>
       <c r="C122" s="89" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D122" s="89" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E122" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F122" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G122" s="89" t="inlineStr">
@@ -25054,7 +25335,7 @@
       </c>
       <c r="H122" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I122" s="112" t="n"/>
@@ -25410,22 +25691,22 @@
       <c r="G142" s="244" t="n"/>
       <c r="H142" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I142" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J142" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K142" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
       <c r="L142" s="111" t="n"/>
@@ -25807,22 +26088,22 @@
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E3" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F3" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -25832,7 +26113,7 @@
       </c>
       <c r="H3" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I3" s="111" t="n"/>
@@ -26201,22 +26482,22 @@
       <c r="G24" s="244" t="n"/>
       <c r="H24" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I24" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J24" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K24" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
       <c r="L24" s="111" t="n"/>
@@ -26527,22 +26808,22 @@
       <c r="B43" s="58" t="n"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D43" s="59" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E43" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -26552,7 +26833,7 @@
       </c>
       <c r="H43" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I43" s="111" t="n"/>
@@ -26921,22 +27202,22 @@
       <c r="G64" s="244" t="n"/>
       <c r="H64" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I64" s="85" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J64" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K64" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
       <c r="L64" s="111" t="n"/>
@@ -27247,22 +27528,22 @@
       <c r="B83" s="88" t="n"/>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D83" s="89" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F83" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G83" s="89" t="inlineStr">
@@ -27272,7 +27553,7 @@
       </c>
       <c r="H83" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I83" s="111" t="n"/>
@@ -27628,22 +27909,22 @@
       <c r="G103" s="244" t="n"/>
       <c r="H103" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I103" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J103" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K103" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
       <c r="L103" s="111" t="n"/>
@@ -27954,22 +28235,22 @@
       <c r="B122" s="88" t="n"/>
       <c r="C122" s="89" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D122" s="89" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E122" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F122" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G122" s="89" t="inlineStr">
@@ -27979,7 +28260,7 @@
       </c>
       <c r="H122" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I122" s="112" t="n"/>
@@ -28335,22 +28616,22 @@
       <c r="G142" s="244" t="n"/>
       <c r="H142" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I142" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J142" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K142" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
       <c r="L142" s="111" t="n"/>
@@ -28732,22 +29013,22 @@
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E3" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F3" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -28757,7 +29038,7 @@
       </c>
       <c r="H3" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I3" s="111" t="n"/>
@@ -29126,22 +29407,22 @@
       <c r="G24" s="244" t="n"/>
       <c r="H24" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I24" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J24" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K24" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
       <c r="L24" s="111" t="n"/>
@@ -29452,22 +29733,22 @@
       <c r="B43" s="58" t="n"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D43" s="59" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E43" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -29477,7 +29758,7 @@
       </c>
       <c r="H43" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I43" s="111" t="n"/>
@@ -29846,22 +30127,22 @@
       <c r="G64" s="244" t="n"/>
       <c r="H64" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I64" s="85" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J64" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K64" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
       <c r="L64" s="111" t="n"/>
@@ -30172,22 +30453,22 @@
       <c r="B83" s="88" t="n"/>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D83" s="89" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F83" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G83" s="89" t="inlineStr">
@@ -30197,7 +30478,7 @@
       </c>
       <c r="H83" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I83" s="111" t="n"/>
@@ -30553,22 +30834,22 @@
       <c r="G103" s="244" t="n"/>
       <c r="H103" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I103" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J103" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K103" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
       <c r="L103" s="111" t="n"/>
@@ -30879,22 +31160,22 @@
       <c r="B122" s="88" t="n"/>
       <c r="C122" s="89" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Algebraic Expressions</t>
         </is>
       </c>
       <c r="D122" s="89" t="inlineStr">
         <is>
-          <t>Equations &amp; Inequalites</t>
+          <t>Equations &amp; Inequalities</t>
         </is>
       </c>
       <c r="E122" s="89" t="inlineStr">
         <is>
-          <t>Patterns</t>
+          <t>Number Patterns</t>
         </is>
       </c>
       <c r="F122" s="89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance, Growth &amp; Decay</t>
         </is>
       </c>
       <c r="G122" s="89" t="inlineStr">
@@ -30904,7 +31185,7 @@
       </c>
       <c r="H122" s="89" t="inlineStr">
         <is>
-          <t>Functions</t>
+          <t>Functions &amp; Graphs</t>
         </is>
       </c>
       <c r="I122" s="112" t="n"/>
@@ -31260,22 +31541,22 @@
       <c r="G142" s="244" t="n"/>
       <c r="H142" s="236" t="inlineStr">
         <is>
-          <t>Identities</t>
+          <t>Identities &amp; Reduction Formulae</t>
         </is>
       </c>
       <c r="I142" s="73" t="inlineStr">
         <is>
-          <t>Equations</t>
+          <t>General Solution &amp; Equations</t>
         </is>
       </c>
       <c r="J142" s="236" t="inlineStr">
         <is>
-          <t>2D &amp; 3D</t>
+          <t>Problems in 2D &amp; 3D</t>
         </is>
       </c>
       <c r="K142" s="74" t="inlineStr">
         <is>
-          <t>Trig Functions</t>
+          <t>Trigonometric Graphs</t>
         </is>
       </c>
       <c r="L142" s="111" t="n"/>
